--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1728,6 +1728,23 @@
       <c r="C81" t="inlineStr">
         <is>
           <t>2026-07-17 10:20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:10:25</t>
         </is>
       </c>
     </row>
@@ -1992,13 +2009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FF1DC37-7E6A-46D2-84DA-2E0F4B63C274}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{326B79A8-B920-4D60-BC5F-58F52017DB63}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EE1F8C9-6195-49A9-BC68-8587A82C248B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBF59B44-1E11-48A7-9A50-00A98666B820}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89BA33C-CF99-44E6-BA00-C441FFC81A15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A53959-4EE7-4237-96B0-F035652FB820}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1745,6 +1745,23 @@
       <c r="C82" t="inlineStr">
         <is>
           <t>2026-07-28 09:10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-28 14:28:47</t>
         </is>
       </c>
     </row>
@@ -2009,13 +2026,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{326B79A8-B920-4D60-BC5F-58F52017DB63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03E2BBB3-4AC5-4681-90A7-E21F5C5FE73B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBF59B44-1E11-48A7-9A50-00A98666B820}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA61A68-F937-481E-920F-6E2945697F41}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43A53959-4EE7-4237-96B0-F035652FB820}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D756F8CC-C43A-424A-86CD-1CE8B4BF3839}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1762,6 +1762,40 @@
       <c r="C83" t="inlineStr">
         <is>
           <t>2026-07-28 14:28:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-12 15:21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:11:28</t>
         </is>
       </c>
     </row>
@@ -2026,13 +2060,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03E2BBB3-4AC5-4681-90A7-E21F5C5FE73B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70B384CA-ED94-4278-86BF-3FD5B66B097F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA61A68-F937-481E-920F-6E2945697F41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D37883-EC89-4EAE-8B93-E9AFF8DDF024}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D756F8CC-C43A-424A-86CD-1CE8B4BF3839}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C11CF8E0-4A78-45B4-ABDE-93EACBAABC89}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1796,6 +1796,23 @@
       <c r="C85" t="inlineStr">
         <is>
           <t>2026-08-12 16:11:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:22:06</t>
         </is>
       </c>
     </row>
@@ -2060,13 +2077,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70B384CA-ED94-4278-86BF-3FD5B66B097F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F72ED2-CF4A-4E33-BB0A-66F23172B437}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14D37883-EC89-4EAE-8B93-E9AFF8DDF024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DD71280-F56A-40F0-9F92-A79DFD963F80}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C11CF8E0-4A78-45B4-ABDE-93EACBAABC89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F56C9877-8DA4-4F2A-B6D0-C762AB1C26F8}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1813,6 +1813,23 @@
       <c r="C86" t="inlineStr">
         <is>
           <t>2026-08-12 16:22:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-17 14:01:04</t>
         </is>
       </c>
     </row>
@@ -2077,13 +2094,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F72ED2-CF4A-4E33-BB0A-66F23172B437}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96406227-2C76-4CED-BE33-80D18DDE6A27}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DD71280-F56A-40F0-9F92-A79DFD963F80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2283D243-1C54-4095-95E1-BC646EFCA0B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F56C9877-8DA4-4F2A-B6D0-C762AB1C26F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4659B21-9158-4D24-B8A1-DD9EF57068F6}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1830,6 +1830,40 @@
       <c r="C87" t="inlineStr">
         <is>
           <t>2026-08-17 14:01:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:28:02</t>
         </is>
       </c>
     </row>
@@ -2094,13 +2128,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96406227-2C76-4CED-BE33-80D18DDE6A27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5569AB65-2B1C-4E32-BAA6-EDB6D6655000}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2283D243-1C54-4095-95E1-BC646EFCA0B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D98D27F-21EA-46B6-A807-76FB86EFB121}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4659B21-9158-4D24-B8A1-DD9EF57068F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E8CED7-5CFC-4317-85AE-6055DAF665AE}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1864,6 +1864,108 @@
       <c r="C89" t="inlineStr">
         <is>
           <t>2026-08-20 16:28:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:01:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:50:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:54:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:15:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:21:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:24:15</t>
         </is>
       </c>
     </row>
@@ -2128,13 +2230,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5569AB65-2B1C-4E32-BAA6-EDB6D6655000}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19F3D82A-78B5-455E-8588-AC3DB4ED2B50}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D98D27F-21EA-46B6-A807-76FB86EFB121}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE1D5E3-BADC-4992-9AF3-C505BBF4CE82}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E8CED7-5CFC-4317-85AE-6055DAF665AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0818D763-1A10-4260-B197-C9F105AC309F}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1966,6 +1966,57 @@
       <c r="C95" t="inlineStr">
         <is>
           <t>2026-09-03 13:24:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:17:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:03:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:09:45</t>
         </is>
       </c>
     </row>
@@ -2230,13 +2281,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19F3D82A-78B5-455E-8588-AC3DB4ED2B50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0181BB4E-B80A-46FB-9911-69BA34CEBDE0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE1D5E3-BADC-4992-9AF3-C505BBF4CE82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C51D5B0-D29E-4912-849E-F664BF62B078}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0818D763-1A10-4260-B197-C9F105AC309F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A9B98F-B1D6-4937-BE25-31E65529BFB9}"/>
 </file>